--- a/oko/config oko.xlsx
+++ b/oko/config oko.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vrln.sharepoint.com/sites/GGD-ONDZ/PSchijf/Gezondheidsmonitor/Algemeen/Automatisering en R/0. Github/report_excel_to_powerpoint/oko/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1133" documentId="13_ncr:1_{BEF9BC84-22C2-4587-9B7D-81FBCE0907AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CC38DC0-B101-4F41-906F-9EC679CF0B09}"/>
+  <xr:revisionPtr revIDLastSave="1474" documentId="13_ncr:1_{BEF9BC84-22C2-4587-9B7D-81FBCE0907AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4C4DAB5-AE11-4AC8-AEDE-97F3A5ECD059}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{340DDFAE-1A83-41FC-A379-531A17E4526A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{340DDFAE-1A83-41FC-A379-531A17E4526A}"/>
   </bookViews>
   <sheets>
     <sheet name="reports" sheetId="4" r:id="rId1"/>
@@ -641,7 +641,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="461">
   <si>
     <t>type</t>
   </si>
@@ -1862,6 +1862,168 @@
   </si>
   <si>
     <t>0 = (Zeer) slechte of gaat wel mentale gezondheid; 1 = (Zeer) goede mentale gezondheid</t>
+  </si>
+  <si>
+    <t>PBMGK3S5</t>
+  </si>
+  <si>
+    <t>0 = Laag emotioneel welbevinden; 1 = Matig tot hoog emotioneel welbevinden</t>
+  </si>
+  <si>
+    <t>Heeft een matig tot hoog emotioneel welbevinden</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en emotioneel welbevinden</t>
+  </si>
+  <si>
+    <t>Middelengebruik en emotioneel welbevinden</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en wekelijks vapen</t>
+  </si>
+  <si>
+    <t>Middelengebruik en wekelijks vapen</t>
+  </si>
+  <si>
+    <t>0 = Vapet niet wekelijks; 1 = Vapet wekelijks</t>
+  </si>
+  <si>
+    <t>Voelt zich veilig op school</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en veilig voelen op school</t>
+  </si>
+  <si>
+    <t>Middelengebruik en veilig voelen op school</t>
+  </si>
+  <si>
+    <t>SOOSK3A1</t>
+  </si>
+  <si>
+    <t>Vindt dat leerlingen op school goed met elkaar omgaan</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en omgang leerlingen</t>
+  </si>
+  <si>
+    <t>Middelengebruik en omgang leerlingen</t>
+  </si>
+  <si>
+    <t>SOOSK3A2</t>
+  </si>
+  <si>
+    <t>Vindt dat docenten op school goed met de leerlingen omgaan</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en omgang docenten</t>
+  </si>
+  <si>
+    <t>Middelengebruik en omgang docenten</t>
+  </si>
+  <si>
+    <t>SOOSK3A3</t>
+  </si>
+  <si>
+    <t>Vindt school (hartstikke) leuk</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en school leuk vinden</t>
+  </si>
+  <si>
+    <t>Middelengebruik en school leuk vinden</t>
+  </si>
+  <si>
+    <t>SBOSK3S7</t>
+  </si>
+  <si>
+    <t>0 = Vindt school vreselijk, niet leuk of gaat wel; 1 = Vindt school (harstikke) leuk</t>
+  </si>
+  <si>
+    <t>Ouders hebben met sommige of meeste ouders van vrienden contact</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en contact ouders</t>
+  </si>
+  <si>
+    <t>Middelengebruik en contact ouders</t>
+  </si>
+  <si>
+    <t>0 = Ouders hebben geen contact met ouders van vrienden; 1 = hebben met sommige of meeste ouders van vrienden contact</t>
+  </si>
+  <si>
+    <t>Ouders maken met ouders van vrienden afspraken over tijd thuis</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en afspraken ouders over tijd thuis</t>
+  </si>
+  <si>
+    <t>Middelengebruik en afspraken ouders over tijd thuis</t>
+  </si>
+  <si>
+    <t>SOCHK3S5</t>
+  </si>
+  <si>
+    <t>0 =Ouders maken met ouders van vrienden geen afspraken over tijd thuis; 1 = Ouders maken met ouders van vrienden afspraken over tijd thuis</t>
+  </si>
+  <si>
+    <t>Ouders maken met ouders van vrienden afspraken over alcohol</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en afspraken ouders over alcohol</t>
+  </si>
+  <si>
+    <t>Middelengebruik en afspraken ouders over alcohol</t>
+  </si>
+  <si>
+    <t>0 =Ouders maken met ouders van vrienden geen afspraken over alcohol; 1 = Ouders maken met ouders van vrienden afspraken over alcohol</t>
+  </si>
+  <si>
+    <t>Chillt 1 keer per maand of vaker ergens zonder aanwezigheid van volwassenen</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en chillen zonder toezicht</t>
+  </si>
+  <si>
+    <t>Middelengebruik en chillen zonder toezicht</t>
+  </si>
+  <si>
+    <t>0 =Chillt minder dan 1 keer per maand ergens zonder aanwezigheid van volwassenen; 1 = Chillt 1 keer per maand of vaker ergens zonder aanwezigheid van volwassenen</t>
+  </si>
+  <si>
+    <t>Meeste tot (bijna) alle vriend(innen) drinken alcohol</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en alcoholgebruik vrienden</t>
+  </si>
+  <si>
+    <t>Middelengebruik en alcoholgebruik vrienden</t>
+  </si>
+  <si>
+    <t>0 = Sommige of geen vriend(innen) drinken alcohol; 1 = Meeste tot (bijna) alle vriend(innen) drinken alcohol</t>
+  </si>
+  <si>
+    <t>Kan bij ouder(s) of verzorger(s) terecht bij een probleem of als diegene ergens mee zit</t>
+  </si>
+  <si>
+    <t>Mentale gezondheid en bij ouders terecht kunnen</t>
+  </si>
+  <si>
+    <t>Middelengebruik en bij ouders terecht kunnen</t>
+  </si>
+  <si>
+    <t>GBZOK3S12</t>
+  </si>
+  <si>
+    <t>0 = Kan niet bij ouder(s) of verzorger(s) terecht bij een probleem of als diegene ergens mee zit; 1 = Kan bij ouder(s) of verzorger(s) terecht bij een probleem of als diegene ergens mee zit</t>
+  </si>
+  <si>
+    <t>0 = Vindt dat docenten op school goed met de leerlingen omgaan (helemaal oneens, oneens of neutraal); 1 = Vindt dat docenten op school goed met de leerlingen omgaan (eens en helemaal eens)</t>
+  </si>
+  <si>
+    <t>0 = Vindt dat leerlingen op school goed met elkaar omgaan (helemaal oneens, oneens of neutraal); 1 = Vindt dat leerlingen op school goed met elkaar omgaan (eens en helemaal eens)</t>
+  </si>
+  <si>
+    <t>0 = Voelt zich veilig op school (helemaal oneens, oneens of neutraal); 1 = Voelt zich veilig op school (eens en helemaal eens)</t>
   </si>
 </sst>
 </file>
@@ -1945,12 +2107,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1978,7 +2146,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2030,6 +2198,12 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2044,6 +2218,30 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2641,22 +2839,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0AA7A9-459B-4958-BBC2-94F84CFD8846}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" style="4" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.44140625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="4"/>
+    <col min="3" max="3" width="27.5703125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
@@ -2688,7 +2886,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>235</v>
       </c>
@@ -2717,7 +2915,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>235</v>
       </c>
@@ -2757,33 +2955,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{784B8C6B-747D-4246-8EF4-E1910EE284AD}">
   <dimension ref="A1:U71"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="80.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="32.109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.88671875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="80.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="32.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="17" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.33203125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="47.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="31.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="47.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>12</v>
       </c>
@@ -2848,7 +3046,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -2871,7 +3069,7 @@
       <c r="P2" s="2"/>
       <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -2893,7 +3091,7 @@
       </c>
       <c r="S3" s="2"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -2920,7 +3118,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>44</v>
       </c>
@@ -2949,7 +3147,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
@@ -2984,7 +3182,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>239</v>
       </c>
@@ -3013,7 +3211,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>239</v>
       </c>
@@ -3048,7 +3246,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>161</v>
       </c>
@@ -3077,7 +3275,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>161</v>
       </c>
@@ -3112,7 +3310,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>109</v>
       </c>
@@ -3147,7 +3345,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>49</v>
       </c>
@@ -3182,7 +3380,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>61</v>
       </c>
@@ -3220,7 +3418,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>50</v>
       </c>
@@ -3255,7 +3453,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>145</v>
       </c>
@@ -3284,7 +3482,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>168</v>
       </c>
@@ -3313,7 +3511,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>169</v>
       </c>
@@ -3342,7 +3540,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>111</v>
       </c>
@@ -3377,7 +3575,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>111</v>
       </c>
@@ -3412,7 +3610,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>261</v>
       </c>
@@ -3441,7 +3639,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>147</v>
       </c>
@@ -3477,7 +3675,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>206</v>
       </c>
@@ -3513,7 +3711,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>59</v>
       </c>
@@ -3551,7 +3749,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>60</v>
       </c>
@@ -3589,7 +3787,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>172</v>
       </c>
@@ -3618,7 +3816,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>175</v>
       </c>
@@ -3647,7 +3845,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>67</v>
       </c>
@@ -3682,7 +3880,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>68</v>
       </c>
@@ -3717,7 +3915,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>250</v>
       </c>
@@ -3752,7 +3950,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>204</v>
       </c>
@@ -3788,7 +3986,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>205</v>
       </c>
@@ -3824,7 +4022,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>77</v>
       </c>
@@ -3853,7 +4051,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>78</v>
       </c>
@@ -3891,7 +4089,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>105</v>
       </c>
@@ -3926,7 +4124,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>104</v>
       </c>
@@ -3961,7 +4159,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>106</v>
       </c>
@@ -3996,7 +4194,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>239</v>
       </c>
@@ -4034,7 +4232,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>148</v>
       </c>
@@ -4072,7 +4270,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>259</v>
       </c>
@@ -4107,7 +4305,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>80</v>
       </c>
@@ -4136,7 +4334,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>125</v>
       </c>
@@ -4165,7 +4363,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>240</v>
       </c>
@@ -4194,7 +4392,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>241</v>
       </c>
@@ -4223,7 +4421,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>125</v>
       </c>
@@ -4258,7 +4456,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>242</v>
       </c>
@@ -4293,7 +4491,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>141</v>
       </c>
@@ -4337,7 +4535,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>141</v>
       </c>
@@ -4381,7 +4579,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>87</v>
       </c>
@@ -4410,7 +4608,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>126</v>
       </c>
@@ -4445,7 +4643,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>127</v>
       </c>
@@ -4478,7 +4676,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>127</v>
       </c>
@@ -4513,7 +4711,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="69" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>145</v>
       </c>
@@ -4551,7 +4749,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>123</v>
       </c>
@@ -4589,7 +4787,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>192</v>
       </c>
@@ -4627,7 +4825,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>189</v>
       </c>
@@ -4665,7 +4863,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>68</v>
       </c>
@@ -4703,7 +4901,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>243</v>
       </c>
@@ -4738,7 +4936,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>146</v>
       </c>
@@ -4776,7 +4974,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>239</v>
       </c>
@@ -4814,7 +5012,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>128</v>
       </c>
@@ -4849,7 +5047,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>93</v>
       </c>
@@ -4884,7 +5082,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>94</v>
       </c>
@@ -4913,7 +5111,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>95</v>
       </c>
@@ -4942,7 +5140,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>184</v>
       </c>
@@ -4971,7 +5169,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>183</v>
       </c>
@@ -5000,7 +5198,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>150</v>
       </c>
@@ -5035,7 +5233,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>112</v>
       </c>
@@ -5070,7 +5268,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>143</v>
       </c>
@@ -5108,7 +5306,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>144</v>
       </c>
@@ -5137,7 +5335,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>145</v>
       </c>
@@ -5175,7 +5373,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>239</v>
       </c>
@@ -5243,35 +5441,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6BEB4C1-A925-4FAE-9007-19794D9EEA69}">
-  <dimension ref="A1:V87"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V137"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="73.88671875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="32.109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.6640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="73.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="32.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="17" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" style="15" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="3" customWidth="1"/>
-    <col min="15" max="15" width="23.5546875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="31.33203125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="47.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="23.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="31.28515625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="47.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>12</v>
       </c>
@@ -5339,7 +5537,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>276</v>
       </c>
@@ -5356,7 +5554,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>279</v>
       </c>
@@ -5373,8 +5571,8 @@
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>282</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -5408,8 +5606,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>282</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -5446,8 +5644,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>286</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -5493,8 +5691,8 @@
         <v>291</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>292</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -5540,8 +5738,8 @@
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>296</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -5575,8 +5773,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>296</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -5613,8 +5811,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
         <v>297</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -5660,8 +5858,8 @@
         <v>291</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>299</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -5707,8 +5905,8 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>302</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -5742,8 +5940,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>302</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -5780,8 +5978,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
         <v>303</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -5827,8 +6025,8 @@
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+    <row r="15" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>305</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -5874,269 +6072,281 @@
         <v>291</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+    <row r="16" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="29"/>
+      <c r="G16" s="20"/>
+      <c r="J16" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K16" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L16" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20">
+        <v>6</v>
+      </c>
+      <c r="O16" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="P16" s="27" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="29"/>
+      <c r="F17" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="G17" s="20"/>
+      <c r="J17" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K17" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L17" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20">
+        <v>6</v>
+      </c>
+      <c r="O17" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="P17" s="27" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="J18" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K18" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20">
+        <v>6</v>
+      </c>
+      <c r="O18" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="P18" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q18" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T18" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="V18" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
+        <v>413</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="J19" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K19" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20">
+        <v>6</v>
+      </c>
+      <c r="O19" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="P19" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q19" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T19" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="V19" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="G20" s="20"/>
+      <c r="J20" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K20" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L20" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="27">
+        <v>7</v>
+      </c>
+      <c r="O20" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="P20" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="S20" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="T20" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="G21" s="20"/>
+      <c r="J21" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K21" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L21" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="27">
+        <v>7</v>
+      </c>
+      <c r="O21" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="P21" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="S21" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="T21" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D22" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="J16" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K16" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N16" s="3">
-        <v>6</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
-        <v>308</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K17" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N17" s="3">
-        <v>6</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K18" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N18" s="3">
-        <v>6</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K19" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N19" s="3">
-        <v>6</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K20" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N20" s="3">
-        <v>7</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K21" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N21" s="3">
-        <v>7</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>321</v>
-      </c>
+      <c r="F22" s="9"/>
       <c r="J22" s="2" t="s">
         <v>156</v>
       </c>
@@ -6147,42 +6357,33 @@
         <v>97</v>
       </c>
       <c r="N22" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>309</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
-        <v>322</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>308</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>314</v>
+        <v>252</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>321</v>
+        <v>34</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>156</v>
@@ -6194,33 +6395,39 @@
         <v>97</v>
       </c>
       <c r="N23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>309</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
-        <v>323</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>310</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>163</v>
+        <v>311</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>34</v>
+        <v>96</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>156</v>
@@ -6238,27 +6445,36 @@
         <v>309</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
-        <v>323</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>313</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>157</v>
+        <v>98</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>156</v>
@@ -6276,33 +6492,27 @@
         <v>309</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>285</v>
+        <v>295</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="19" t="s">
-        <v>324</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>316</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>327</v>
+        <v>34</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>156</v>
@@ -6314,42 +6524,33 @@
         <v>97</v>
       </c>
       <c r="N26" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>309</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="19" t="s">
-        <v>328</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>316</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>327</v>
+        <v>34</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>156</v>
@@ -6361,33 +6562,39 @@
         <v>97</v>
       </c>
       <c r="N27" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>309</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="s">
-        <v>329</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>318</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>225</v>
+      <c r="C28" s="9" t="s">
+        <v>319</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>34</v>
+        <v>96</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>156</v>
@@ -6402,33 +6609,39 @@
         <v>9</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
-        <v>329</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
+        <v>322</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>225</v>
+      <c r="C29" s="9" t="s">
+        <v>314</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>157</v>
+        <v>98</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>156</v>
@@ -6443,130 +6656,112 @@
         <v>9</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="P29" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K30" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N30" s="3">
+        <v>10</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K31" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N31" s="3">
+        <v>10</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="P31" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="T29" s="2" t="s">
+      <c r="T31" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="V29" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K30" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N30" s="3">
-        <v>9</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K31" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N31" s="3">
-        <v>9</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
-        <v>336</v>
+    </row>
+    <row r="32" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="21" t="s">
+        <v>324</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>223</v>
+      <c r="C32" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>34</v>
+        <v>96</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>156</v>
@@ -6581,33 +6776,39 @@
         <v>10</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
-        <v>336</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
+        <v>328</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>223</v>
+      <c r="C33" s="9" t="s">
+        <v>314</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>157</v>
+        <v>98</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>156</v>
@@ -6622,219 +6823,212 @@
         <v>10</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="P33" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="32" t="s">
+        <v>409</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="29"/>
+      <c r="G34" s="20"/>
+      <c r="J34" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K34" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L34" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20">
+        <v>11</v>
+      </c>
+      <c r="O34" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="P34" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="T34" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="32" t="s">
+        <v>409</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="29"/>
+      <c r="F35" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="G35" s="20"/>
+      <c r="J35" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K35" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L35" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20">
+        <v>11</v>
+      </c>
+      <c r="O35" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="P35" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="T35" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V33" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="9" t="s">
+    </row>
+    <row r="36" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="32" t="s">
+        <v>410</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D36" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E36" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K34" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L34" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N34" s="3">
-        <v>10</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P34" s="2" t="s">
+      <c r="F36" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="J36" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K36" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L36" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20">
+        <v>11</v>
+      </c>
+      <c r="O36" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="P36" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q34" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T34" s="2" t="s">
+      <c r="Q36" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T36" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V34" s="2" t="s">
+      <c r="V36" s="27" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="9" t="s">
+    <row r="37" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="32" t="s">
+        <v>411</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D37" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E37" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K35" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L35" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N35" s="3">
-        <v>10</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P35" s="2" t="s">
+      <c r="F37" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="J37" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K37" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L37" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20">
+        <v>11</v>
+      </c>
+      <c r="O37" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="P37" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q35" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T35" s="2" t="s">
+      <c r="Q37" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T37" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V35" s="2" t="s">
+      <c r="V37" s="27" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A36" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D36" s="18" t="s">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D38" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K36" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L36" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N36" s="3">
-        <v>11</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A37" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K37" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L37" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N37" s="3">
-        <v>11</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="T37" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>156</v>
       </c>
@@ -6845,45 +7039,36 @@
         <v>97</v>
       </c>
       <c r="N38" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>330</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>291</v>
+        <v>103</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="20" t="s">
-        <v>343</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" s="22" t="s">
+        <v>329</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>314</v>
+      <c r="C39" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>315</v>
+        <v>34</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>342</v>
+        <v>157</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>156</v>
@@ -6895,36 +7080,42 @@
         <v>97</v>
       </c>
       <c r="N39" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>330</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>97</v>
+        <v>285</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>291</v>
+        <v>103</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A40" s="21" t="s">
-        <v>344</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
+        <v>332</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>345</v>
+      <c r="C40" s="9" t="s">
+        <v>287</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>34</v>
+        <v>98</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>333</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>156</v>
@@ -6939,33 +7130,42 @@
         <v>12</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>103</v>
+        <v>291</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
-        <v>344</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A41" s="22" t="s">
+        <v>335</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>345</v>
+      <c r="C41" s="9" t="s">
+        <v>314</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>157</v>
+        <v>98</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>333</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>156</v>
@@ -6980,130 +7180,121 @@
         <v>12</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="P41" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K42" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N42" s="3">
+        <v>13</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K43" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N43" s="3">
+        <v>13</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="P43" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="T41" s="2" t="s">
+      <c r="T43" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="V41" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="s">
-        <v>348</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" s="9" t="s">
+      <c r="V43" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A44" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D44" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K42" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L42" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N42" s="3">
-        <v>12</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K43" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L43" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N43" s="3">
-        <v>12</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V43" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A44" s="22" t="s">
-        <v>351</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>34</v>
+      <c r="F44" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>338</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>156</v>
@@ -7118,33 +7309,42 @@
         <v>13</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>103</v>
+        <v>291</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>352</v>
+      <c r="C45" s="9" t="s">
+        <v>314</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>157</v>
+        <v>98</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>338</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>156</v>
@@ -7159,130 +7359,121 @@
         <v>13</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="P45" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K46" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L46" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N46" s="3">
+        <v>14</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K47" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N47" s="3">
+        <v>14</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="P47" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="T45" s="2" t="s">
+      <c r="T47" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="V45" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" s="9" t="s">
+      <c r="V47" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D48" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E48" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K46" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L46" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N46" s="3">
-        <v>13</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T46" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V46" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K47" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L47" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N47" s="3">
-        <v>13</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V47" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>34</v>
+      <c r="F48" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>156</v>
@@ -7297,33 +7488,42 @@
         <v>14</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>103</v>
+        <v>291</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>356</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="22" t="s">
+        <v>343</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>357</v>
+      <c r="C49" s="9" t="s">
+        <v>314</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>157</v>
+        <v>98</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>156</v>
@@ -7338,1562 +7538,1617 @@
         <v>14</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="P49" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="26" t="s">
+        <v>453</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>456</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50" s="29"/>
+      <c r="G50" s="20"/>
+      <c r="J50" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K50" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L50" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20">
+        <v>15</v>
+      </c>
+      <c r="O50" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P50" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="T50" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="V50" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>453</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>456</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="G51" s="20"/>
+      <c r="J51" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K51" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L51" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M51" s="20"/>
+      <c r="N51" s="20">
+        <v>15</v>
+      </c>
+      <c r="O51" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P51" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T49" s="2" t="s">
+      <c r="T51" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V49" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C50" s="9" t="s">
+      <c r="V51" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="26" t="s">
+        <v>454</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D52" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E52" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K50" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L50" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N50" s="3">
-        <v>14</v>
-      </c>
-      <c r="O50" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P50" s="2" t="s">
+      <c r="F52" s="27" t="s">
+        <v>456</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="J52" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K52" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L52" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20">
+        <v>15</v>
+      </c>
+      <c r="O52" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P52" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T50" s="2" t="s">
+      <c r="Q52" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T52" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V50" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" s="9" t="s">
+      <c r="V52" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="26" t="s">
+        <v>455</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D53" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E53" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K51" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L51" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N51" s="3">
-        <v>14</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P51" s="2" t="s">
+      <c r="F53" s="27" t="s">
+        <v>456</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="J53" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K53" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L53" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M53" s="20"/>
+      <c r="N53" s="20">
+        <v>15</v>
+      </c>
+      <c r="O53" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P53" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T51" s="2" t="s">
+      <c r="Q53" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T53" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V51" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A52" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D52" s="18" t="s">
+      <c r="V53" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="D54" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J52" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K52" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L52" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N52" s="3">
-        <v>15</v>
-      </c>
-      <c r="O52" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P52" s="2" t="s">
+      <c r="E54" s="29"/>
+      <c r="G54" s="20"/>
+      <c r="J54" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K54" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L54" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M54" s="20"/>
+      <c r="N54" s="20">
+        <v>16</v>
+      </c>
+      <c r="O54" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P54" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="T52" s="2" t="s">
+      <c r="T54" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V52" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A53" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D53" s="18" t="s">
+      <c r="V54" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="D55" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="E55" s="29"/>
+      <c r="F55" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="J53" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K53" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L53" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N53" s="3">
-        <v>15</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P53" s="2" t="s">
+      <c r="G55" s="20"/>
+      <c r="J55" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K55" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L55" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20">
+        <v>16</v>
+      </c>
+      <c r="O55" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P55" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T53" s="2" t="s">
+      <c r="T55" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V53" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C54" s="9" t="s">
+      <c r="V55" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
+        <v>433</v>
+      </c>
+      <c r="B56" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D56" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E56" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K54" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L54" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N54" s="3">
-        <v>15</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P54" s="2" t="s">
+      <c r="F56" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="G56" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="J56" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K56" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L56" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M56" s="20"/>
+      <c r="N56" s="20">
+        <v>16</v>
+      </c>
+      <c r="O56" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P56" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q54" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T54" s="2" t="s">
+      <c r="Q56" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T56" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V54" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" s="9" t="s">
+      <c r="V56" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D57" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E57" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K55" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L55" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N55" s="3">
-        <v>15</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P55" s="2" t="s">
+      <c r="F57" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="J57" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K57" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L57" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M57" s="20"/>
+      <c r="N57" s="20">
+        <v>16</v>
+      </c>
+      <c r="O57" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P57" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q55" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T55" s="2" t="s">
+      <c r="Q57" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T57" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V55" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D56" s="18" t="s">
+      <c r="V57" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="D58" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J56" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K56" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L56" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N56" s="3">
-        <v>16</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P56" s="2" t="s">
+      <c r="E58" s="29"/>
+      <c r="G58" s="20"/>
+      <c r="J58" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K58" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L58" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M58" s="20"/>
+      <c r="N58" s="20">
+        <v>17</v>
+      </c>
+      <c r="O58" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P58" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="T56" s="2" t="s">
+      <c r="T58" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V56" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D57" s="18" t="s">
+      <c r="V58" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="B59" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="D59" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="E59" s="29"/>
+      <c r="F59" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="J57" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K57" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L57" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N57" s="3">
-        <v>16</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P57" s="2" t="s">
+      <c r="G59" s="20"/>
+      <c r="J59" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K59" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L59" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M59" s="20"/>
+      <c r="N59" s="20">
+        <v>17</v>
+      </c>
+      <c r="O59" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P59" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T57" s="2" t="s">
+      <c r="T59" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V57" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" ht="69" x14ac:dyDescent="0.3">
-      <c r="A58" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C58" s="9" t="s">
+      <c r="V59" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A60" s="26" t="s">
+        <v>437</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D60" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E60" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K58" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L58" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N58" s="3">
-        <v>16</v>
-      </c>
-      <c r="O58" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P58" s="2" t="s">
+      <c r="F60" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="G60" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="J60" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K60" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L60" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M60" s="20"/>
+      <c r="N60" s="20">
+        <v>17</v>
+      </c>
+      <c r="O60" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P60" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T58" s="2" t="s">
+      <c r="Q60" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T60" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V58" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" ht="69" x14ac:dyDescent="0.3">
-      <c r="A59" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C59" s="9" t="s">
+      <c r="V60" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A61" s="26" t="s">
+        <v>438</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D61" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E61" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K59" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L59" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N59" s="3">
-        <v>16</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="P59" s="2" t="s">
+      <c r="F61" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="J61" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K61" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L61" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M61" s="20"/>
+      <c r="N61" s="20">
+        <v>17</v>
+      </c>
+      <c r="O61" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P61" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q59" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T59" s="2" t="s">
+      <c r="Q61" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T61" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V59" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A60" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="D60" s="18" t="s">
+      <c r="V61" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="26" t="s">
+        <v>441</v>
+      </c>
+      <c r="B62" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J60" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K60" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L60" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N60" s="3">
-        <v>17</v>
-      </c>
-      <c r="O60" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P60" s="2" t="s">
+      <c r="E62" s="29"/>
+      <c r="G62" s="20"/>
+      <c r="J62" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K62" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L62" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M62" s="20"/>
+      <c r="N62" s="20">
+        <v>18</v>
+      </c>
+      <c r="O62" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P62" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="T60" s="2" t="s">
+      <c r="T62" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V60" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A61" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C61" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="D61" s="18" t="s">
+      <c r="V62" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>441</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C63" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="D63" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="E63" s="29"/>
+      <c r="F63" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="J61" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K61" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L61" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N61" s="3">
-        <v>17</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P61" s="2" t="s">
+      <c r="G63" s="20"/>
+      <c r="J63" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K63" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L63" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20">
+        <v>18</v>
+      </c>
+      <c r="O63" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P63" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T61" s="2" t="s">
+      <c r="T63" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V61" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C62" s="9" t="s">
+      <c r="V63" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A64" s="26" t="s">
+        <v>442</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="D64" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E64" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K62" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L62" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N62" s="3">
-        <v>17</v>
-      </c>
-      <c r="O62" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P62" s="2" t="s">
+      <c r="F64" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="G64" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="J64" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K64" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L64" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20">
+        <v>18</v>
+      </c>
+      <c r="O64" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P64" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q62" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T62" s="2" t="s">
+      <c r="Q64" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T64" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V62" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C63" s="9" t="s">
+      <c r="V64" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A65" s="26" t="s">
+        <v>443</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D65" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E65" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K63" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L63" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N63" s="3">
-        <v>17</v>
-      </c>
-      <c r="O63" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P63" s="2" t="s">
+      <c r="F65" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="G65" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="J65" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K65" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L65" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20">
+        <v>18</v>
+      </c>
+      <c r="O65" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P65" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q63" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T63" s="2" t="s">
+      <c r="Q65" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T65" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V63" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A64" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C64" s="23" t="s">
-        <v>381</v>
-      </c>
-      <c r="D64" s="18" t="s">
+      <c r="V65" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="26" t="s">
+        <v>445</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="D66" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J64" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K64" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L64" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N64" s="3">
-        <v>18</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P64" s="2" t="s">
+      <c r="E66" s="29"/>
+      <c r="G66" s="20"/>
+      <c r="J66" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K66" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L66" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M66" s="20"/>
+      <c r="N66" s="20">
+        <v>19</v>
+      </c>
+      <c r="O66" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P66" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="T64" s="2" t="s">
+      <c r="T66" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V64" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A65" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C65" s="23" t="s">
-        <v>381</v>
-      </c>
-      <c r="D65" s="18" t="s">
+      <c r="V66" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="26" t="s">
+        <v>445</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C67" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="D67" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="E67" s="29"/>
+      <c r="F67" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="J65" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K65" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L65" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N65" s="3">
-        <v>18</v>
-      </c>
-      <c r="O65" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P65" s="2" t="s">
+      <c r="G67" s="20"/>
+      <c r="J67" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K67" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L67" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M67" s="20"/>
+      <c r="N67" s="20">
+        <v>19</v>
+      </c>
+      <c r="O67" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P67" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T65" s="2" t="s">
+      <c r="T67" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V65" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C66" s="9" t="s">
+      <c r="V67" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="26" t="s">
+        <v>446</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D68" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E68" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K66" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L66" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N66" s="3">
-        <v>18</v>
-      </c>
-      <c r="O66" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P66" s="2" t="s">
+      <c r="F68" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="G68" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="J68" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K68" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L68" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M68" s="20"/>
+      <c r="N68" s="20">
+        <v>19</v>
+      </c>
+      <c r="O68" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P68" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q66" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T66" s="2" t="s">
+      <c r="Q68" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T68" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V66" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C67" s="9" t="s">
+      <c r="V68" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>447</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D69" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E69" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K67" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L67" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N67" s="3">
-        <v>18</v>
-      </c>
-      <c r="O67" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P67" s="2" t="s">
+      <c r="F69" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="G69" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="J69" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K69" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L69" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M69" s="20"/>
+      <c r="N69" s="20">
+        <v>19</v>
+      </c>
+      <c r="O69" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="P69" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q67" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T67" s="2" t="s">
+      <c r="Q69" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T69" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V67" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="D68" s="18" t="s">
+      <c r="V69" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="33" t="s">
+        <v>415</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="D70" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J68" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K68" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L68" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N68" s="3">
-        <v>19</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P68" s="2" t="s">
+      <c r="E70" s="29"/>
+      <c r="G70" s="20"/>
+      <c r="J70" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K70" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L70" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M70" s="20"/>
+      <c r="N70" s="20">
+        <v>20</v>
+      </c>
+      <c r="O70" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P70" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="T68" s="2" t="s">
+      <c r="T70" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V68" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="D69" s="18" t="s">
+      <c r="V70" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="33" t="s">
+        <v>415</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="D71" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="E71" s="29"/>
+      <c r="F71" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="J69" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K69" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L69" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N69" s="3">
-        <v>19</v>
-      </c>
-      <c r="O69" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P69" s="2" t="s">
+      <c r="G71" s="20"/>
+      <c r="J71" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K71" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L71" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M71" s="20"/>
+      <c r="N71" s="20">
+        <v>20</v>
+      </c>
+      <c r="O71" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P71" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T69" s="2" t="s">
+      <c r="T71" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V69" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A70" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C70" s="9" t="s">
+      <c r="V71" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A72" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C72" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D72" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E72" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K70" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L70" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N70" s="3">
-        <v>19</v>
-      </c>
-      <c r="O70" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P70" s="2" t="s">
+      <c r="F72" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="G72" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="J72" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K72" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L72" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M72" s="20"/>
+      <c r="N72" s="20">
+        <v>20</v>
+      </c>
+      <c r="O72" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P72" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q70" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T70" s="2" t="s">
+      <c r="Q72" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T72" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V70" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C71" s="9" t="s">
+      <c r="V72" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+      <c r="A73" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C73" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D73" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E73" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K71" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L71" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N71" s="3">
-        <v>19</v>
-      </c>
-      <c r="O71" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P71" s="2" t="s">
+      <c r="F73" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="J73" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K73" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L73" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M73" s="20"/>
+      <c r="N73" s="20">
+        <v>20</v>
+      </c>
+      <c r="O73" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P73" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q71" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T71" s="2" t="s">
+      <c r="Q73" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T73" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V71" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C72" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="D72" s="18" t="s">
+      <c r="V73" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C74" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="D74" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J72" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K72" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L72" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N72" s="3">
-        <v>20</v>
-      </c>
-      <c r="O72" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P72" s="2" t="s">
+      <c r="E74" s="29"/>
+      <c r="G74" s="20"/>
+      <c r="J74" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K74" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L74" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M74" s="20"/>
+      <c r="N74" s="20">
+        <v>21</v>
+      </c>
+      <c r="O74" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P74" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="T72" s="2" t="s">
+      <c r="T74" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V72" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="D73" s="18" t="s">
+      <c r="V74" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C75" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="D75" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="E75" s="29"/>
+      <c r="F75" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="J73" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K73" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L73" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N73" s="3">
-        <v>20</v>
-      </c>
-      <c r="O73" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P73" s="2" t="s">
+      <c r="G75" s="20"/>
+      <c r="J75" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K75" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L75" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M75" s="20"/>
+      <c r="N75" s="20">
+        <v>21</v>
+      </c>
+      <c r="O75" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P75" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T73" s="2" t="s">
+      <c r="T75" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V73" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C74" s="9" t="s">
+      <c r="V75" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="33" t="s">
+        <v>420</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D74" s="18" t="s">
+      <c r="D76" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E76" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K74" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L74" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N74" s="3">
-        <v>20</v>
-      </c>
-      <c r="O74" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P74" s="2" t="s">
+      <c r="F76" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="G76" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="J76" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K76" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L76" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M76" s="20"/>
+      <c r="N76" s="20">
+        <v>21</v>
+      </c>
+      <c r="O76" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P76" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q74" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T74" s="2" t="s">
+      <c r="Q76" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T76" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V74" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C75" s="9" t="s">
+      <c r="V76" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C77" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D75" s="18" t="s">
+      <c r="D77" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E77" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K75" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L75" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N75" s="3">
-        <v>20</v>
-      </c>
-      <c r="O75" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P75" s="2" t="s">
+      <c r="F77" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="G77" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="J77" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K77" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L77" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M77" s="20"/>
+      <c r="N77" s="20">
+        <v>21</v>
+      </c>
+      <c r="O77" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P77" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q75" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T75" s="2" t="s">
+      <c r="Q77" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T77" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V75" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A76" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C76" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="D76" s="18" t="s">
+      <c r="V77" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="33" t="s">
+        <v>423</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C78" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="D78" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J76" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K76" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L76" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N76" s="3">
-        <v>21</v>
-      </c>
-      <c r="O76" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P76" s="2" t="s">
+      <c r="E78" s="29"/>
+      <c r="G78" s="20"/>
+      <c r="J78" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K78" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L78" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M78" s="20"/>
+      <c r="N78" s="20">
+        <v>22</v>
+      </c>
+      <c r="O78" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P78" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="T76" s="2" t="s">
+      <c r="T78" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V76" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A77" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C77" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="D77" s="18" t="s">
+      <c r="V78" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="33" t="s">
+        <v>423</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C79" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="D79" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="E79" s="29"/>
+      <c r="F79" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="J77" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K77" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L77" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N77" s="3">
-        <v>21</v>
-      </c>
-      <c r="O77" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P77" s="2" t="s">
+      <c r="G79" s="20"/>
+      <c r="J79" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K79" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L79" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M79" s="20"/>
+      <c r="N79" s="20">
+        <v>22</v>
+      </c>
+      <c r="O79" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P79" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="T77" s="2" t="s">
+      <c r="T79" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="V77" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C78" s="9" t="s">
+      <c r="V79" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" s="27" customFormat="1" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C80" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="D78" s="18" t="s">
+      <c r="D80" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E80" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K78" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L78" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N78" s="3">
-        <v>21</v>
-      </c>
-      <c r="O78" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P78" s="2" t="s">
+      <c r="F80" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="G80" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="J80" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K80" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L80" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M80" s="20"/>
+      <c r="N80" s="20">
+        <v>22</v>
+      </c>
+      <c r="O80" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P80" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="Q78" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T78" s="2" t="s">
+      <c r="Q80" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T80" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V78" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A79" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C79" s="9" t="s">
+      <c r="V80" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" s="27" customFormat="1" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="33" t="s">
+        <v>425</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C81" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="D81" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E81" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K79" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L79" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N79" s="3">
-        <v>21</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P79" s="2" t="s">
+      <c r="F81" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="G81" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="J81" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K81" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L81" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M81" s="20"/>
+      <c r="N81" s="20">
+        <v>22</v>
+      </c>
+      <c r="O81" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P81" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="Q79" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T79" s="2" t="s">
+      <c r="Q81" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T81" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="V79" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A80" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C80" s="23" t="s">
-        <v>396</v>
-      </c>
-      <c r="D80" s="18" t="s">
+      <c r="V81" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A82" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D82" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K80" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L80" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N80" s="3">
-        <v>22</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P80" s="2" t="s">
+      <c r="J82" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K82" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L82" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N82" s="3">
+        <v>23</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="P82" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="T80" s="2" t="s">
+      <c r="T82" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A81" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C81" s="23" t="s">
-        <v>396</v>
-      </c>
-      <c r="D81" s="18" t="s">
+      <c r="V82" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D83" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="F83" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="J81" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K81" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L81" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N81" s="3">
-        <v>22</v>
-      </c>
-      <c r="O81" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P81" s="2" t="s">
+      <c r="J83" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K83" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L83" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N83" s="3">
+        <v>23</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="P83" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="T81" s="2" t="s">
+      <c r="T83" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="V81" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A82" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C82" s="9" t="s">
+      <c r="V83" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A84" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C84" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="D82" s="18" t="s">
+      <c r="D84" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E84" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="J82" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K82" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L82" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N82" s="3">
-        <v>22</v>
-      </c>
-      <c r="O82" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P82" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q82" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T82" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V82" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A83" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K83" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L83" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N83" s="3">
-        <v>22</v>
-      </c>
-      <c r="O83" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P83" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q83" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T83" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A84" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C84" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>34</v>
+      <c r="F84" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>156</v>
@@ -8908,33 +9163,42 @@
         <v>23</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>103</v>
+        <v>291</v>
       </c>
       <c r="V84" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A85" s="20" t="s">
-        <v>398</v>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="23" t="s">
+        <v>404</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C85" s="23" t="s">
-        <v>399</v>
+      <c r="C85" s="9" t="s">
+        <v>314</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>34</v>
+        <v>98</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>315</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>157</v>
+        <v>345</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>156</v>
@@ -8949,134 +9213,2380 @@
         <v>23</v>
       </c>
       <c r="O85" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q85" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T85" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="33" t="s">
+        <v>427</v>
+      </c>
+      <c r="B86" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C86" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="D86" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E86" s="29"/>
+      <c r="G86" s="20"/>
+      <c r="J86" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K86" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L86" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M86" s="20"/>
+      <c r="N86" s="20">
+        <v>24</v>
+      </c>
+      <c r="O86" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P86" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="T86" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="V86" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="33" t="s">
+        <v>427</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C87" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="D87" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E87" s="29"/>
+      <c r="F87" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="G87" s="20"/>
+      <c r="J87" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K87" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L87" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M87" s="20"/>
+      <c r="N87" s="20">
+        <v>24</v>
+      </c>
+      <c r="O87" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P87" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="T87" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="V87" s="27" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="B88" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E88" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="F88" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J88" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K88" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L88" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M88" s="20"/>
+      <c r="N88" s="20">
+        <v>24</v>
+      </c>
+      <c r="O88" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P88" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q88" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T88" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="V88" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A89" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="D89" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="F89" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="G89" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J89" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K89" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L89" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M89" s="20"/>
+      <c r="N89" s="20">
+        <v>24</v>
+      </c>
+      <c r="O89" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="P89" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q89" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T89" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="V89" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K90" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L90" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N90" s="3">
+        <v>25</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T90" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K91" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L91" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N91" s="3">
+        <v>25</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T91" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V91" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A92" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K92" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L92" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N92" s="3">
+        <v>25</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q92" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T92" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K93" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L93" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N93" s="3">
+        <v>25</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q93" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T93" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V93" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K94" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L94" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N94" s="3">
+        <v>26</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T94" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V94" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K95" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L95" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N95" s="3">
+        <v>26</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T95" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V95" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K96" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L96" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N96" s="3">
+        <v>26</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q96" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T96" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V96" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D97" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K97" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L97" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N97" s="3">
+        <v>26</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q97" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T97" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A98" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D98" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K98" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L98" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N98" s="3">
+        <v>27</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T98" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V98" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A99" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D99" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K99" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L99" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N99" s="3">
+        <v>27</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T99" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V99" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A100" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K100" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L100" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N100" s="3">
+        <v>27</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q100" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T100" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V100" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A101" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D101" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K101" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L101" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N101" s="3">
+        <v>27</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q101" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T101" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V101" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K102" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L102" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N102" s="3">
+        <v>28</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T102" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A103" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K103" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L103" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N103" s="3">
+        <v>28</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T103" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V103" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K104" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L104" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N104" s="3">
+        <v>28</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q104" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T104" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K105" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L105" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N105" s="3">
+        <v>28</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="P105" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q105" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T105" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V105" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="26" t="s">
+        <v>449</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C106" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="D106" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E106" s="29"/>
+      <c r="G106" s="20"/>
+      <c r="J106" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K106" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L106" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M106" s="20"/>
+      <c r="N106" s="20">
+        <v>29</v>
+      </c>
+      <c r="O106" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="P106" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="T106" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="V106" s="27" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="26" t="s">
+        <v>449</v>
+      </c>
+      <c r="B107" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C107" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="D107" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E107" s="29"/>
+      <c r="F107" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="G107" s="20"/>
+      <c r="J107" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K107" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L107" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M107" s="20"/>
+      <c r="N107" s="20">
+        <v>29</v>
+      </c>
+      <c r="O107" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="P107" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="T107" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="V107" s="27" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="26" t="s">
+        <v>450</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D108" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E108" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="F108" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="G108" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="J108" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K108" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L108" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M108" s="20"/>
+      <c r="N108" s="20">
+        <v>29</v>
+      </c>
+      <c r="O108" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="P108" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q108" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T108" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="V108" s="27" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="D109" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E109" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="F109" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="G109" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="J109" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K109" s="30">
+        <v>2025</v>
+      </c>
+      <c r="L109" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M109" s="20"/>
+      <c r="N109" s="20">
+        <v>29</v>
+      </c>
+      <c r="O109" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="P109" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q109" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="T109" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="V109" s="27" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A110" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K110" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L110" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N110" s="3">
+        <v>30</v>
+      </c>
+      <c r="O110" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="P85" s="2" t="s">
+      <c r="P110" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T110" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V110" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A111" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C111" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="D111" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K111" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L111" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N111" s="3">
+        <v>30</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P111" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="T85" s="2" t="s">
+      <c r="T111" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="V85" s="2" t="s">
+      <c r="V111" s="2" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="86" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="20" t="s">
+    <row r="112" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A112" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D112" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K112" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L112" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N112" s="3">
+        <v>30</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P112" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q112" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T112" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V112" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A113" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D113" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K113" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L113" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N113" s="3">
+        <v>30</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T113" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V113" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A114" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="D114" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K114" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L114" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N114" s="3">
+        <v>31</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T114" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V114" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A115" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="D115" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K115" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L115" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N115" s="3">
+        <v>31</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T115" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V115" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A116" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D116" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K116" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L116" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N116" s="3">
+        <v>31</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P116" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q116" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T116" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V116" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D117" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K117" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L117" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N117" s="3">
+        <v>31</v>
+      </c>
+      <c r="O117" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P117" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q117" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T117" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V117" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A118" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="D118" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K118" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L118" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N118" s="3">
+        <v>32</v>
+      </c>
+      <c r="O118" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P118" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T118" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V118" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A119" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C119" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K119" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L119" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N119" s="3">
+        <v>32</v>
+      </c>
+      <c r="O119" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P119" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T119" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V119" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" ht="51" x14ac:dyDescent="0.25">
+      <c r="A120" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D120" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K120" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L120" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N120" s="3">
+        <v>32</v>
+      </c>
+      <c r="O120" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P120" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q120" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T120" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V120" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22" ht="51" x14ac:dyDescent="0.25">
+      <c r="A121" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K121" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L121" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N121" s="3">
+        <v>32</v>
+      </c>
+      <c r="O121" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P121" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q121" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T121" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V121" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A122" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C122" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K122" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L122" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N122" s="3">
+        <v>33</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P122" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T122" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V122" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="D123" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K123" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L123" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N123" s="3">
+        <v>33</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P123" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T123" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V123" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" ht="51" x14ac:dyDescent="0.25">
+      <c r="A124" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D124" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K124" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L124" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N124" s="3">
+        <v>33</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P124" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q124" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T124" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V124" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22" ht="51" x14ac:dyDescent="0.25">
+      <c r="A125" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K125" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L125" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N125" s="3">
+        <v>33</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P125" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q125" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T125" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V125" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A126" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C126" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K126" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L126" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N126" s="3">
+        <v>34</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P126" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T126" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V126" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A127" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C127" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D127" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K127" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L127" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N127" s="3">
+        <v>34</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P127" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T127" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V127" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="22" t="s">
         <v>392</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C86" s="9" t="s">
+      <c r="B128" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C128" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="D86" s="18" t="s">
+      <c r="D128" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E128" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="F128" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K128" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L128" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N128" s="3">
+        <v>34</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P128" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q128" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T128" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V128" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A129" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D129" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K129" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L129" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N129" s="3">
+        <v>34</v>
+      </c>
+      <c r="O129" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P129" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q129" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T129" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V129" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A130" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C130" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="D130" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K130" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L130" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N130" s="3">
+        <v>35</v>
+      </c>
+      <c r="O130" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P130" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T130" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V130" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A131" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C131" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="D131" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K131" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L131" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N131" s="3">
+        <v>35</v>
+      </c>
+      <c r="O131" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P131" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T131" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V131" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A132" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D132" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K132" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L132" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N132" s="3">
+        <v>35</v>
+      </c>
+      <c r="O132" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P132" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q132" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T132" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V132" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A133" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K133" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L133" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N133" s="3">
+        <v>35</v>
+      </c>
+      <c r="O133" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P133" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q133" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T133" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="V133" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A134" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C134" s="25" t="s">
         <v>399</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="D134" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K134" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L134" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N134" s="3">
+        <v>36</v>
+      </c>
+      <c r="O134" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P134" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="T134" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V134" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A135" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C135" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="D135" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K135" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L135" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N135" s="3">
+        <v>36</v>
+      </c>
+      <c r="O135" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="P135" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="T135" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V135" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A136" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D136" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G136" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="J86" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K86" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L86" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N86" s="3">
-        <v>23</v>
-      </c>
-      <c r="O86" s="2" t="s">
+      <c r="J136" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K136" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L136" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N136" s="3">
+        <v>36</v>
+      </c>
+      <c r="O136" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="P86" s="2" t="s">
+      <c r="P136" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="Q86" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T86" s="2" t="s">
+      <c r="Q136" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T136" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="V86" s="2" t="s">
+      <c r="V136" s="2" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="87" spans="1:22" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A87" s="20" t="s">
+    <row r="137" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A137" s="22" t="s">
         <v>394</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C87" s="9" t="s">
+      <c r="B137" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C137" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="D87" s="18" t="s">
+      <c r="D137" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E137" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F137" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="G137" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="J87" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K87" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L87" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N87" s="3">
-        <v>23</v>
-      </c>
-      <c r="O87" s="2" t="s">
+      <c r="J137" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K137" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L137" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N137" s="3">
+        <v>36</v>
+      </c>
+      <c r="O137" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="P87" s="2" t="s">
+      <c r="P137" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="Q87" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="T87" s="2" t="s">
+      <c r="Q137" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T137" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="V87" s="2" t="s">
+      <c r="V137" s="2" t="s">
         <v>378</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576" xr:uid="{C6EB7205-4D37-4C9B-997D-26E82B583491}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q19 Q22:Q1048576" xr:uid="{C6EB7205-4D37-4C9B-997D-26E82B583491}">
       <formula1>"none"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U19 U22:U1048576" xr:uid="{234B6A15-FB77-401C-B3E9-D16BB4EEFA29}">
+      <formula1>"high, low, nextTo, none"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R20:R21 S2:S1048576" xr:uid="{BE59BD8D-4E15-4E03-86E7-7290FF5F90FD}">
+      <formula1>"horizontal"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{257BAA86-065F-4DCE-BD2C-9B09E549017F}">
       <formula1>"none, dim, var"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576" xr:uid="{234B6A15-FB77-401C-B3E9-D16BB4EEFA29}">
-      <formula1>"high, low, nextTo, none"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576" xr:uid="{7DB5FCC8-124C-4CD3-9A44-1964C52B91E0}">
       <formula1>"b, tr, l, r, t, n"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576" xr:uid="{BE59BD8D-4E15-4E03-86E7-7290FF5F90FD}">
-      <formula1>"horizontal"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9086,7 +11596,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C4EA295FB1FB9547A73C9F5819D6E613" ma:contentTypeVersion="22" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="586e6f9b10cb27d3f03483507ae7cb9d">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C4EA295FB1FB9547A73C9F5819D6E613" ma:contentTypeVersion="23" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="fb09b8f9996d29818860aca561f17aea">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4e95bed8-6d15-4403-ad70-a53422338dca" xmlns:ns3="10d3344f-2d16-43d9-a145-97142f5cb288" xmlns:ns4="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f29125cba2118f3064d103e6e0ba85ce" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="4e95bed8-6d15-4403-ad70-a53422338dca"/>
@@ -9396,7 +11906,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15B2EAB0-CF1E-4BFF-A0B2-760E3129F1CF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FE7204C-46E3-4193-934C-CAD2C90BC68A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>

--- a/oko/config oko.xlsx
+++ b/oko/config oko.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vrln.sharepoint.com/sites/GGD-ONDZ/PSchijf/Gezondheidsmonitor/Algemeen/Automatisering en R/0. Github/report_excel_to_powerpoint/oko/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vrln-my.sharepoint.com/personal/s_vermeulen_vrln_nl/Documents/Bureaublad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1474" documentId="13_ncr:1_{BEF9BC84-22C2-4587-9B7D-81FBCE0907AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4C4DAB5-AE11-4AC8-AEDE-97F3A5ECD059}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0502DA0-ACB5-42E5-B257-4A46D080BA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{340DDFAE-1A83-41FC-A379-531A17E4526A}"/>
+    <workbookView xWindow="-23148" yWindow="4152" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{340DDFAE-1A83-41FC-A379-531A17E4526A}"/>
   </bookViews>
   <sheets>
     <sheet name="reports" sheetId="4" r:id="rId1"/>
@@ -641,7 +641,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="462">
   <si>
     <t>type</t>
   </si>
@@ -1273,12 +1273,6 @@
     <t>x_ticklabel_position</t>
   </si>
   <si>
-    <t>LBRAA303; LBGEA306</t>
-  </si>
-  <si>
-    <t>LBRAA304; LBGEA305</t>
-  </si>
-  <si>
     <t>SOROK3A7</t>
   </si>
   <si>
@@ -1525,9 +1519,6 @@
     <t>LBRAK3S19; LBSDK3S1</t>
   </si>
   <si>
-    <t>1 = Rookt wekelijks; 1 = Ooit wiet gebruikt</t>
-  </si>
-  <si>
     <t>Grafiek 4</t>
   </si>
   <si>
@@ -1546,9 +1537,6 @@
     <t>LBAGK3S27; LBSDK3S1</t>
   </si>
   <si>
-    <t>1 = Dronken of aangeschoten laatste 4 weken; 1 = Ooit wiet gebruikt</t>
-  </si>
-  <si>
     <t>Heeft ooit wiet of hasj gebruikt</t>
   </si>
   <si>
@@ -1588,9 +1576,6 @@
     <t>LBAGK3S27; LBRAK3S19; LBSDK3S1</t>
   </si>
   <si>
-    <t>1 = Dronken of aangeschoten laatste 4 weken; 1 = Rookt wekelijks; 1 = Ooit wiet gebruikt</t>
-  </si>
-  <si>
     <t>Was in de laatste 4 weken vaak tot altijd eenzaam</t>
   </si>
   <si>
@@ -1606,9 +1591,6 @@
     <t>1 =(Zeer) goede mentale gezondheid; 1 = (Zeer) vaak gestrest</t>
   </si>
   <si>
-    <t>0 = Nooit tot soms eenzaam; 1 = Vaak tot altijd eenzaam</t>
-  </si>
-  <si>
     <t>Middelengebruik en eenzaamheid</t>
   </si>
   <si>
@@ -1741,24 +1723,15 @@
     <t>Mentale gezondheid en 's avonds niet thuis</t>
   </si>
   <si>
-    <t>0 = Minder dan 3 dagen na 22:00 uur niet thuis; 1 = 3 dagen of meer na 22:00 uur niet thuis</t>
-  </si>
-  <si>
     <t>Middelengebruik en 's avonds niet thuis</t>
   </si>
   <si>
-    <t>3 of meer dagen in de afgelopen week 's avonds na 10 uur niet thuis en ouders/verzorgers weten nooit/soms waar je bent</t>
-  </si>
-  <si>
     <t>SOROK3S6</t>
   </si>
   <si>
     <t>Mentale gezondheid en niet thuis zonder dat ouders weten waar je bent</t>
   </si>
   <si>
-    <t>0 = Minder dan 3 dagen na 22:00 uur niet thuis en ouders weten niet waar je bent; 1 = 3 dagen of meer na 22:00 uur niet thuis en ouders weten niet waar je bent</t>
-  </si>
-  <si>
     <t>Middelengebruik en niet thuis zonder dat ouders weten waar je bent</t>
   </si>
   <si>
@@ -2024,6 +1997,36 @@
   </si>
   <si>
     <t>0 = Voelt zich veilig op school (helemaal oneens, oneens of neutraal); 1 = Voelt zich veilig op school (eens en helemaal eens)</t>
+  </si>
+  <si>
+    <t>LBRAA305; LBGEA306</t>
+  </si>
+  <si>
+    <t>LBRAA306; LBGEA307</t>
+  </si>
+  <si>
+    <t>0 = Nooit tot soms eenzaam; 1 = Vaak tot altijd eenzaam laatste 4 weken</t>
+  </si>
+  <si>
+    <t>1 = Rookt wekelijks; 1 = Ooit wiet/hasj gebruikt</t>
+  </si>
+  <si>
+    <t>1 = Dronken of aangeschoten laatste 4 weken; 1 = Ooit wiet/hasj gebruikt</t>
+  </si>
+  <si>
+    <t>1 = Dronken of aangeschoten laatste 4 weken; 1 = Rookt wekelijks; 1 = Ooit wiet/hasj gebruikt</t>
+  </si>
+  <si>
+    <t>Kind is 3 dagen of meer pas na 22.00 uur thuis</t>
+  </si>
+  <si>
+    <t>0 = Minder dan 3 dagen na 22:00 uur thuis; 1 = 3 dagen of meer na 22:00 uur thuis</t>
+  </si>
+  <si>
+    <t>3 of meer dagen in de afgelopen week 's avonds na 22 uur niet thuis en ouders/verzorgers weten nooit/soms waar je bent</t>
+  </si>
+  <si>
+    <t>0 = Minder dan 3 dagen na 22:00 uur thuis en ouders weten niet waar je bent; 1 = 3 dagen of meer na 22:00 uur thuis en ouders weten niet waar je bent</t>
   </si>
 </sst>
 </file>
@@ -2888,19 +2891,19 @@
     </row>
     <row r="2" spans="1:10" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>154</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>156</v>
@@ -2917,19 +2920,19 @@
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>156</v>
@@ -2958,7 +2961,7 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="2" customWidth="1"/>
     <col min="3" max="3" width="37.42578125" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.140625" style="12" customWidth="1"/>
     <col min="5" max="5" width="32.140625" style="5" customWidth="1"/>
@@ -3028,7 +3031,7 @@
         <v>20</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>26</v>
@@ -3184,13 +3187,13 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>34</v>
@@ -3213,13 +3216,13 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>34</v>
@@ -3461,7 +3464,7 @@
         <v>33</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>34</v>
@@ -3490,7 +3493,7 @@
         <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>34</v>
@@ -3519,7 +3522,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>34</v>
@@ -3548,7 +3551,7 @@
         <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>98</v>
@@ -3583,7 +3586,7 @@
         <v>36</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>98</v>
@@ -3612,13 +3615,13 @@
     </row>
     <row r="20" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D20" s="18" t="s">
         <v>96</v>
@@ -3647,7 +3650,7 @@
         <v>131</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D21" s="18"/>
       <c r="J21" s="2" t="s">
@@ -3672,7 +3675,7 @@
         <v>97</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3683,7 +3686,7 @@
         <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D22" s="18"/>
       <c r="J22" s="2" t="s">
@@ -3708,7 +3711,7 @@
         <v>97</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="51" x14ac:dyDescent="0.25">
@@ -3719,7 +3722,7 @@
         <v>36</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>170</v>
@@ -3757,13 +3760,13 @@
         <v>36</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D24" s="18" t="s">
         <v>165</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>156</v>
@@ -3853,7 +3856,7 @@
         <v>100</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>114</v>
@@ -3894,7 +3897,7 @@
         <v>96</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>157</v>
@@ -3917,19 +3920,19 @@
     </row>
     <row r="29" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D29" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>157</v>
@@ -3958,11 +3961,11 @@
         <v>131</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>210</v>
+        <v>452</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>156</v>
@@ -3983,7 +3986,7 @@
         <v>108</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3994,11 +3997,11 @@
         <v>131</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>211</v>
+        <v>453</v>
       </c>
       <c r="D31" s="18"/>
       <c r="E31" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>156</v>
@@ -4019,7 +4022,7 @@
         <v>108</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -4059,7 +4062,7 @@
         <v>36</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D33" s="18" t="s">
         <v>177</v>
@@ -4097,7 +4100,7 @@
         <v>36</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>34</v>
@@ -4132,7 +4135,7 @@
         <v>36</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D35" s="18" t="s">
         <v>34</v>
@@ -4167,7 +4170,7 @@
         <v>36</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>34</v>
@@ -4196,22 +4199,22 @@
     </row>
     <row r="37" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>156</v>
@@ -4240,13 +4243,13 @@
         <v>36</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>157</v>
@@ -4272,19 +4275,19 @@
     </row>
     <row r="39" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>157</v>
@@ -4342,7 +4345,7 @@
         <v>33</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D41" s="18" t="s">
         <v>34</v>
@@ -4365,13 +4368,13 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D42" s="18" t="s">
         <v>34</v>
@@ -4394,13 +4397,13 @@
     </row>
     <row r="43" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D43" s="18" t="s">
         <v>34</v>
@@ -4429,7 +4432,7 @@
         <v>36</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D44" s="18" t="s">
         <v>34</v>
@@ -4458,13 +4461,13 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D45" s="18" t="s">
         <v>34</v>
@@ -4508,10 +4511,10 @@
         <v>149</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>156</v>
@@ -4532,7 +4535,7 @@
         <v>108</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
@@ -4552,10 +4555,10 @@
         <v>149</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>156</v>
@@ -4576,7 +4579,7 @@
         <v>108</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4587,7 +4590,7 @@
         <v>33</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>34</v>
@@ -4651,7 +4654,7 @@
         <v>131</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D50" s="18"/>
       <c r="E50" s="5" t="s">
@@ -4676,7 +4679,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>127</v>
       </c>
@@ -4684,7 +4687,7 @@
         <v>36</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D51" s="18" t="s">
         <v>96</v>
@@ -4719,16 +4722,16 @@
         <v>36</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D52" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>157</v>
@@ -4757,13 +4760,13 @@
         <v>36</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D53" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>198</v>
@@ -4801,7 +4804,7 @@
         <v>34</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>199</v>
@@ -4839,7 +4842,7 @@
         <v>34</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>200</v>
@@ -4877,7 +4880,7 @@
         <v>34</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>201</v>
@@ -4903,7 +4906,7 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>100</v>
@@ -4944,13 +4947,13 @@
         <v>36</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>165</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>156</v>
@@ -4976,13 +4979,13 @@
     </row>
     <row r="59" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>34</v>
@@ -4991,7 +4994,7 @@
         <v>203</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>156</v>
@@ -5276,13 +5279,13 @@
         <v>36</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D68" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>156</v>
@@ -5314,7 +5317,7 @@
         <v>33</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D69" s="18" t="s">
         <v>34</v>
@@ -5343,16 +5346,16 @@
         <v>36</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>156</v>
@@ -5375,22 +5378,22 @@
     </row>
     <row r="71" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D71" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>156</v>
@@ -5513,13 +5516,13 @@
         <v>19</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>26</v>
@@ -5539,16 +5542,16 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N2" s="3">
         <v>1</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>32</v>
@@ -5556,30 +5559,30 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N3" s="3">
         <v>2</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>34</v>
@@ -5597,10 +5600,10 @@
         <v>3</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>103</v>
@@ -5608,13 +5611,13 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>34</v>
@@ -5635,10 +5638,10 @@
         <v>3</v>
       </c>
       <c r="O5" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>103</v>
@@ -5646,25 +5649,25 @@
     </row>
     <row r="6" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>156</v>
@@ -5679,39 +5682,39 @@
         <v>3</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>294</v>
+        <v>455</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>156</v>
@@ -5726,21 +5729,21 @@
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>36</v>
@@ -5764,10 +5767,10 @@
         <v>4</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>103</v>
@@ -5775,7 +5778,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
@@ -5802,10 +5805,10 @@
         <v>4</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>103</v>
@@ -5813,25 +5816,25 @@
     </row>
     <row r="10" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>190</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>156</v>
@@ -5846,39 +5849,39 @@
         <v>4</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>301</v>
+        <v>456</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>190</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>156</v>
@@ -5893,21 +5896,21 @@
         <v>4</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>36</v>
@@ -5931,10 +5934,10 @@
         <v>5</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>103</v>
@@ -5942,7 +5945,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>36</v>
@@ -5969,10 +5972,10 @@
         <v>5</v>
       </c>
       <c r="O13" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>103</v>
@@ -5980,25 +5983,25 @@
     </row>
     <row r="14" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>156</v>
@@ -6013,39 +6016,39 @@
         <v>5</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>156</v>
@@ -6060,16 +6063,16 @@
         <v>5</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
@@ -6101,10 +6104,10 @@
         <v>6</v>
       </c>
       <c r="O16" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P16" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
@@ -6139,33 +6142,33 @@
         <v>6</v>
       </c>
       <c r="O17" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P17" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B18" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F18" s="19" t="s">
         <v>191</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="J18" s="27" t="s">
         <v>156</v>
@@ -6181,42 +6184,42 @@
         <v>6</v>
       </c>
       <c r="O18" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P18" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q18" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T18" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V18" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B19" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>191</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="J19" s="27" t="s">
         <v>156</v>
@@ -6232,19 +6235,19 @@
         <v>6</v>
       </c>
       <c r="O19" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P19" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q19" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T19" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V19" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
@@ -6255,7 +6258,7 @@
         <v>36</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>170</v>
@@ -6278,10 +6281,10 @@
         <v>7</v>
       </c>
       <c r="O20" s="27" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P20" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="S20" s="27" t="s">
         <v>102</v>
@@ -6298,13 +6301,13 @@
         <v>36</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>165</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G21" s="20"/>
       <c r="J21" s="27" t="s">
@@ -6321,10 +6324,10 @@
         <v>7</v>
       </c>
       <c r="O21" s="27" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P21" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="S21" s="27" t="s">
         <v>102</v>
@@ -6335,13 +6338,13 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>34</v>
@@ -6360,10 +6363,10 @@
         <v>8</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>103</v>
@@ -6371,13 +6374,13 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>34</v>
@@ -6398,10 +6401,10 @@
         <v>8</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>103</v>
@@ -6409,25 +6412,25 @@
     </row>
     <row r="24" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D24" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>156</v>
@@ -6442,39 +6445,39 @@
         <v>8</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q24" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D25" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>156</v>
@@ -6489,27 +6492,27 @@
         <v>8</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D26" s="18" t="s">
         <v>34</v>
@@ -6527,10 +6530,10 @@
         <v>9</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>103</v>
@@ -6538,13 +6541,13 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>34</v>
@@ -6565,10 +6568,10 @@
         <v>9</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>103</v>
@@ -6576,25 +6579,25 @@
     </row>
     <row r="28" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>321</v>
+        <v>454</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>156</v>
@@ -6609,39 +6612,39 @@
         <v>9</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q28" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D29" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>321</v>
+        <v>454</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>156</v>
@@ -6656,21 +6659,21 @@
         <v>9</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q29" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>36</v>
@@ -6694,10 +6697,10 @@
         <v>10</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>103</v>
@@ -6705,7 +6708,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>36</v>
@@ -6732,10 +6735,10 @@
         <v>10</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>103</v>
@@ -6743,25 +6746,25 @@
     </row>
     <row r="32" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D32" s="18" t="s">
         <v>96</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>156</v>
@@ -6776,39 +6779,39 @@
         <v>10</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q32" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D33" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>163</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>156</v>
@@ -6823,27 +6826,27 @@
         <v>10</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q33" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="32" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B34" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>34</v>
@@ -6864,10 +6867,10 @@
         <v>11</v>
       </c>
       <c r="O34" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P34" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T34" s="27" t="s">
         <v>103</v>
@@ -6875,13 +6878,13 @@
     </row>
     <row r="35" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="32" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B35" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D35" s="28" t="s">
         <v>34</v>
@@ -6905,10 +6908,10 @@
         <v>11</v>
       </c>
       <c r="O35" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P35" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T35" s="27" t="s">
         <v>103</v>
@@ -6916,25 +6919,25 @@
     </row>
     <row r="36" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="32" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B36" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="J36" s="27" t="s">
         <v>156</v>
@@ -6950,42 +6953,42 @@
         <v>11</v>
       </c>
       <c r="O36" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P36" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q36" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T36" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V36" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="37" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="32" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="B37" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="J37" s="27" t="s">
         <v>156</v>
@@ -7001,30 +7004,30 @@
         <v>11</v>
       </c>
       <c r="O37" s="27" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P37" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q37" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T37" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V37" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>34</v>
@@ -7042,27 +7045,27 @@
         <v>12</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>34</v>
@@ -7083,39 +7086,39 @@
         <v>12</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>156</v>
@@ -7130,42 +7133,42 @@
         <v>12</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q40" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D41" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>156</v>
@@ -7180,30 +7183,30 @@
         <v>12</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q41" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D42" s="18" t="s">
         <v>34</v>
@@ -7221,27 +7224,27 @@
         <v>13</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D43" s="18" t="s">
         <v>34</v>
@@ -7262,39 +7265,39 @@
         <v>13</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T43" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D44" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>156</v>
@@ -7309,42 +7312,42 @@
         <v>13</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D45" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>156</v>
@@ -7359,30 +7362,30 @@
         <v>13</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q45" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="22" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>34</v>
@@ -7400,27 +7403,27 @@
         <v>14</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T46" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>34</v>
@@ -7441,39 +7444,39 @@
         <v>14</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>156</v>
@@ -7488,42 +7491,42 @@
         <v>14</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q48" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>156</v>
@@ -7538,30 +7541,30 @@
         <v>14</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q49" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="50" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B50" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D50" s="28" t="s">
         <v>34</v>
@@ -7582,27 +7585,27 @@
         <v>15</v>
       </c>
       <c r="O50" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P50" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T50" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V50" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="51" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B51" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D51" s="28" t="s">
         <v>34</v>
@@ -7626,39 +7629,39 @@
         <v>15</v>
       </c>
       <c r="O51" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P51" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T51" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V51" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="52" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B52" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D52" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="J52" s="27" t="s">
         <v>156</v>
@@ -7674,42 +7677,42 @@
         <v>15</v>
       </c>
       <c r="O52" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P52" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q52" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T52" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V52" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B53" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D53" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="J53" s="27" t="s">
         <v>156</v>
@@ -7725,30 +7728,30 @@
         <v>15</v>
       </c>
       <c r="O53" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P53" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q53" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T53" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V53" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="54" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B54" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D54" s="28" t="s">
         <v>34</v>
@@ -7769,27 +7772,27 @@
         <v>16</v>
       </c>
       <c r="O54" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P54" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T54" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V54" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B55" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D55" s="28" t="s">
         <v>34</v>
@@ -7813,39 +7816,39 @@
         <v>16</v>
       </c>
       <c r="O55" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P55" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T55" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V55" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="B56" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D56" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F56" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="J56" s="27" t="s">
         <v>156</v>
@@ -7861,42 +7864,42 @@
         <v>16</v>
       </c>
       <c r="O56" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P56" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q56" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T56" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V56" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="57" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D57" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E57" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G57" s="20" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="J57" s="27" t="s">
         <v>156</v>
@@ -7912,30 +7915,30 @@
         <v>16</v>
       </c>
       <c r="O57" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P57" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q57" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T57" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V57" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="B58" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D58" s="28" t="s">
         <v>34</v>
@@ -7956,27 +7959,27 @@
         <v>17</v>
       </c>
       <c r="O58" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P58" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T58" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V58" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D59" s="28" t="s">
         <v>34</v>
@@ -8000,39 +8003,39 @@
         <v>17</v>
       </c>
       <c r="O59" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P59" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T59" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V59" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D60" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E60" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="J60" s="27" t="s">
         <v>156</v>
@@ -8048,42 +8051,42 @@
         <v>17</v>
       </c>
       <c r="O60" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P60" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q60" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T60" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V60" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B61" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D61" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E61" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="J61" s="27" t="s">
         <v>156</v>
@@ -8099,30 +8102,30 @@
         <v>17</v>
       </c>
       <c r="O61" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P61" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q61" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T61" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V61" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="B62" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C62" s="27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D62" s="28" t="s">
         <v>34</v>
@@ -8143,27 +8146,27 @@
         <v>18</v>
       </c>
       <c r="O62" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P62" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T62" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V62" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="B63" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D63" s="28" t="s">
         <v>34</v>
@@ -8187,39 +8190,39 @@
         <v>18</v>
       </c>
       <c r="O63" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P63" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T63" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V63" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B64" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D64" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="J64" s="27" t="s">
         <v>156</v>
@@ -8235,42 +8238,42 @@
         <v>18</v>
       </c>
       <c r="O64" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P64" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q64" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T64" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V64" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B65" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D65" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E65" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="J65" s="27" t="s">
         <v>156</v>
@@ -8286,30 +8289,30 @@
         <v>18</v>
       </c>
       <c r="O65" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P65" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q65" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T65" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V65" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B66" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C66" s="27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D66" s="28" t="s">
         <v>34</v>
@@ -8330,27 +8333,27 @@
         <v>19</v>
       </c>
       <c r="O66" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P66" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T66" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V66" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B67" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D67" s="28" t="s">
         <v>34</v>
@@ -8374,39 +8377,39 @@
         <v>19</v>
       </c>
       <c r="O67" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P67" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T67" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V67" s="27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B68" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D68" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F68" s="27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="J68" s="27" t="s">
         <v>156</v>
@@ -8422,42 +8425,42 @@
         <v>19</v>
       </c>
       <c r="O68" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P68" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q68" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T68" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V68" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="B69" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D69" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="J69" s="27" t="s">
         <v>156</v>
@@ -8473,30 +8476,30 @@
         <v>19</v>
       </c>
       <c r="O69" s="27" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P69" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q69" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T69" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V69" s="27" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="33" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B70" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C70" s="27" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D70" s="28" t="s">
         <v>34</v>
@@ -8517,27 +8520,27 @@
         <v>20</v>
       </c>
       <c r="O70" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P70" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T70" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V70" s="27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="33" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B71" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C71" s="27" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D71" s="28" t="s">
         <v>34</v>
@@ -8561,39 +8564,39 @@
         <v>20</v>
       </c>
       <c r="O71" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P71" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T71" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V71" s="27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A72" s="33" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B72" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E72" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F72" s="27" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="J72" s="27" t="s">
         <v>156</v>
@@ -8609,42 +8612,42 @@
         <v>20</v>
       </c>
       <c r="O72" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P72" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q72" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T72" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V72" s="27" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="73" spans="1:22" s="27" customFormat="1" ht="51" x14ac:dyDescent="0.25">
       <c r="A73" s="33" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B73" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D73" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E73" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F73" s="27" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="J73" s="27" t="s">
         <v>156</v>
@@ -8660,30 +8663,30 @@
         <v>20</v>
       </c>
       <c r="O73" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P73" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q73" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T73" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V73" s="27" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="33" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B74" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C74" s="27" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>34</v>
@@ -8704,27 +8707,27 @@
         <v>21</v>
       </c>
       <c r="O74" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P74" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T74" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V74" s="27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="33" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B75" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C75" s="27" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D75" s="28" t="s">
         <v>34</v>
@@ -8748,39 +8751,39 @@
         <v>21</v>
       </c>
       <c r="O75" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P75" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T75" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V75" s="27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A76" s="33" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B76" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D76" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E76" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F76" s="27" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="J76" s="27" t="s">
         <v>156</v>
@@ -8796,42 +8799,42 @@
         <v>21</v>
       </c>
       <c r="O76" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P76" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q76" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T76" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V76" s="27" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="77" spans="1:22" s="27" customFormat="1" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A77" s="33" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B77" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E77" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F77" s="27" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="J77" s="27" t="s">
         <v>156</v>
@@ -8847,30 +8850,30 @@
         <v>21</v>
       </c>
       <c r="O77" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P77" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q77" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T77" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V77" s="27" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="33" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B78" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C78" s="27" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="D78" s="28" t="s">
         <v>34</v>
@@ -8891,27 +8894,27 @@
         <v>22</v>
       </c>
       <c r="O78" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P78" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T78" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V78" s="27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="33" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B79" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="D79" s="28" t="s">
         <v>34</v>
@@ -8935,39 +8938,39 @@
         <v>22</v>
       </c>
       <c r="O79" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P79" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T79" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V79" s="27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:22" s="27" customFormat="1" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B80" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D80" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E80" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F80" s="27" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="J80" s="27" t="s">
         <v>156</v>
@@ -8983,42 +8986,42 @@
         <v>22</v>
       </c>
       <c r="O80" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P80" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q80" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T80" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V80" s="27" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:22" s="27" customFormat="1" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A81" s="33" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="B81" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D81" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E81" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F81" s="27" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="J81" s="27" t="s">
         <v>156</v>
@@ -9034,30 +9037,30 @@
         <v>22</v>
       </c>
       <c r="O81" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P81" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q81" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T81" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V81" s="27" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="23" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D82" s="18" t="s">
         <v>34</v>
@@ -9075,27 +9078,27 @@
         <v>23</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T82" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V82" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="23" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D83" s="18" t="s">
         <v>34</v>
@@ -9116,39 +9119,39 @@
         <v>23</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T83" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V83" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D84" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>156</v>
@@ -9163,42 +9166,42 @@
         <v>23</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q84" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V84" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A85" s="23" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D85" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>156</v>
@@ -9213,30 +9216,30 @@
         <v>23</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q85" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V85" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B86" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="D86" s="28" t="s">
         <v>34</v>
@@ -9257,27 +9260,27 @@
         <v>24</v>
       </c>
       <c r="O86" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P86" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T86" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V86" s="27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="87" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B87" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="D87" s="28" t="s">
         <v>34</v>
@@ -9301,39 +9304,39 @@
         <v>24</v>
       </c>
       <c r="O87" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P87" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T87" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V87" s="27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="B88" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D88" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E88" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="J88" s="27" t="s">
         <v>156</v>
@@ -9349,42 +9352,42 @@
         <v>24</v>
       </c>
       <c r="O88" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P88" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q88" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T88" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V88" s="27" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="89" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A89" s="33" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="B89" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E89" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="J89" s="27" t="s">
         <v>156</v>
@@ -9400,30 +9403,30 @@
         <v>24</v>
       </c>
       <c r="O89" s="27" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P89" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q89" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T89" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V89" s="27" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D90" s="18" t="s">
         <v>34</v>
@@ -9441,27 +9444,27 @@
         <v>25</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T90" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" s="24" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D91" s="18" t="s">
         <v>34</v>
@@ -9482,39 +9485,39 @@
         <v>25</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T91" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V91" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="92" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="24" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D92" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>156</v>
@@ -9529,42 +9532,42 @@
         <v>25</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q92" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T92" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V92" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="93" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="24" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D93" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>156</v>
@@ -9579,30 +9582,30 @@
         <v>25</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q93" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T93" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D94" s="18" t="s">
         <v>34</v>
@@ -9620,27 +9623,27 @@
         <v>26</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T94" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V94" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D95" s="18" t="s">
         <v>34</v>
@@ -9661,39 +9664,39 @@
         <v>26</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T95" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D96" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>156</v>
@@ -9708,42 +9711,42 @@
         <v>26</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T96" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V96" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D97" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>156</v>
@@ -9758,30 +9761,30 @@
         <v>26</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T97" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="s">
-        <v>364</v>
+        <v>458</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D98" s="18" t="s">
         <v>34</v>
@@ -9799,27 +9802,27 @@
         <v>27</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T98" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V98" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="22" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D99" s="18" t="s">
         <v>34</v>
@@ -9840,39 +9843,39 @@
         <v>27</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T99" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="100" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A100" s="22" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D100" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>366</v>
+        <v>459</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>156</v>
@@ -9887,42 +9890,42 @@
         <v>27</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q100" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T100" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="101" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="22" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D101" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>366</v>
+        <v>459</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>156</v>
@@ -9937,30 +9940,30 @@
         <v>27</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q101" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T101" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="102" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A102" s="22" t="s">
-        <v>368</v>
+        <v>460</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D102" s="18" t="s">
         <v>34</v>
@@ -9978,27 +9981,27 @@
         <v>28</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T102" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A103" s="22" t="s">
-        <v>368</v>
+        <v>460</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D103" s="18" t="s">
         <v>34</v>
@@ -10019,39 +10022,39 @@
         <v>28</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T103" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V103" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="104" spans="1:22" ht="63.75" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" ht="51" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D104" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>371</v>
+        <v>461</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>156</v>
@@ -10066,42 +10069,42 @@
         <v>28</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q104" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T104" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="105" spans="1:22" ht="63.75" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" ht="51" x14ac:dyDescent="0.25">
       <c r="A105" s="22" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D105" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>371</v>
+        <v>461</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>156</v>
@@ -10116,30 +10119,30 @@
         <v>28</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q105" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T105" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V105" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="26" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B106" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C106" s="27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D106" s="28" t="s">
         <v>34</v>
@@ -10160,27 +10163,27 @@
         <v>29</v>
       </c>
       <c r="O106" s="27" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P106" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T106" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V106" s="27" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B107" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C107" s="27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D107" s="28" t="s">
         <v>34</v>
@@ -10204,39 +10207,39 @@
         <v>29</v>
       </c>
       <c r="O107" s="27" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P107" s="27" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T107" s="27" t="s">
         <v>103</v>
       </c>
       <c r="V107" s="27" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="108" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A108" s="26" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B108" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D108" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E108" s="29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F108" s="27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J108" s="27" t="s">
         <v>156</v>
@@ -10252,42 +10255,42 @@
         <v>29</v>
       </c>
       <c r="O108" s="27" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P108" s="27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q108" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T108" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V108" s="27" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:22" s="27" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B109" s="27" t="s">
         <v>36</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D109" s="28" t="s">
         <v>98</v>
       </c>
       <c r="E109" s="29" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F109" s="27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J109" s="27" t="s">
         <v>156</v>
@@ -10303,30 +10306,30 @@
         <v>29</v>
       </c>
       <c r="O109" s="27" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P109" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q109" s="27" t="s">
         <v>97</v>
       </c>
       <c r="T109" s="27" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V109" s="27" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" s="22" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C110" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D110" s="18" t="s">
         <v>34</v>
@@ -10344,27 +10347,27 @@
         <v>30</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T110" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111" s="22" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D111" s="18" t="s">
         <v>34</v>
@@ -10385,39 +10388,39 @@
         <v>30</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T111" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V111" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A112" s="22" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D112" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>156</v>
@@ -10432,42 +10435,42 @@
         <v>30</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q112" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T112" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V112" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="113" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A113" s="22" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D113" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>156</v>
@@ -10482,30 +10485,30 @@
         <v>30</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q113" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T113" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114" s="22" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D114" s="18" t="s">
         <v>34</v>
@@ -10523,27 +10526,27 @@
         <v>31</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T114" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115" s="22" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D115" s="18" t="s">
         <v>34</v>
@@ -10564,39 +10567,39 @@
         <v>31</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T115" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A116" s="22" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D116" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>156</v>
@@ -10611,42 +10614,42 @@
         <v>31</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q116" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T116" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V116" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A117" s="22" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D117" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>156</v>
@@ -10661,30 +10664,30 @@
         <v>31</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q117" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T117" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A118" s="22" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C118" s="25" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D118" s="18" t="s">
         <v>34</v>
@@ -10702,27 +10705,27 @@
         <v>32</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T118" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A119" s="22" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C119" s="25" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D119" s="18" t="s">
         <v>34</v>
@@ -10743,39 +10746,39 @@
         <v>32</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T119" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:22" ht="51" x14ac:dyDescent="0.25">
       <c r="A120" s="22" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D120" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>156</v>
@@ -10790,42 +10793,42 @@
         <v>32</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q120" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T120" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V120" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:22" ht="51" x14ac:dyDescent="0.25">
       <c r="A121" s="22" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D121" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>156</v>
@@ -10840,30 +10843,30 @@
         <v>32</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q121" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T121" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V121" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="122" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A122" s="22" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C122" s="25" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D122" s="18" t="s">
         <v>34</v>
@@ -10881,27 +10884,27 @@
         <v>33</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T122" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V122" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123" spans="1:22" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A123" s="22" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C123" s="25" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D123" s="18" t="s">
         <v>34</v>
@@ -10922,39 +10925,39 @@
         <v>33</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P123" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T123" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V123" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="124" spans="1:22" ht="51" x14ac:dyDescent="0.25">
       <c r="A124" s="22" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D124" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>156</v>
@@ -10969,42 +10972,42 @@
         <v>33</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q124" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T124" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V124" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="1:22" ht="51" x14ac:dyDescent="0.25">
       <c r="A125" s="22" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D125" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>156</v>
@@ -11019,30 +11022,30 @@
         <v>33</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P125" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q125" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T125" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V125" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126" s="22" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C126" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D126" s="18" t="s">
         <v>34</v>
@@ -11060,27 +11063,27 @@
         <v>34</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P126" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T126" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V126" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127" s="22" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C127" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D127" s="18" t="s">
         <v>34</v>
@@ -11101,39 +11104,39 @@
         <v>34</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P127" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T127" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V127" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="128" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A128" s="22" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D128" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>156</v>
@@ -11148,42 +11151,42 @@
         <v>34</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q128" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T128" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V128" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="129" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A129" s="22" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D129" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>156</v>
@@ -11198,30 +11201,30 @@
         <v>34</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P129" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q129" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T129" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V129" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="130" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A130" s="22" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C130" s="25" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D130" s="18" t="s">
         <v>34</v>
@@ -11239,27 +11242,27 @@
         <v>35</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P130" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T130" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V130" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="131" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A131" s="22" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C131" s="25" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D131" s="18" t="s">
         <v>34</v>
@@ -11280,39 +11283,39 @@
         <v>35</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P131" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T131" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V131" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="132" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A132" s="22" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D132" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>156</v>
@@ -11327,42 +11330,42 @@
         <v>35</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P132" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="Q132" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T132" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V132" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="133" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A133" s="22" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D133" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>156</v>
@@ -11377,30 +11380,30 @@
         <v>35</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P133" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q133" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T133" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V133" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A134" s="22" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C134" s="25" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D134" s="18" t="s">
         <v>34</v>
@@ -11418,27 +11421,27 @@
         <v>36</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P134" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T134" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V134" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A135" s="22" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C135" s="25" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D135" s="18" t="s">
         <v>34</v>
@@ -11459,89 +11462,89 @@
         <v>36</v>
       </c>
       <c r="O135" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P135" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T135" s="2" t="s">
         <v>103</v>
       </c>
       <c r="V135" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="136" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A136" s="22" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D136" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E136" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K136" s="17">
+        <v>2025</v>
+      </c>
+      <c r="L136" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N136" s="3">
+        <v>36</v>
+      </c>
+      <c r="O136" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="P136" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F136" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="J136" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K136" s="17">
-        <v>2025</v>
-      </c>
-      <c r="L136" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="N136" s="3">
-        <v>36</v>
-      </c>
-      <c r="O136" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="P136" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="Q136" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T136" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V136" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="137" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A137" s="22" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D137" s="18" t="s">
         <v>98</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>315</v>
+        <v>457</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>156</v>
@@ -11556,19 +11559,19 @@
         <v>36</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="P137" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q137" s="2" t="s">
         <v>97</v>
       </c>
       <c r="T137" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V137" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -11596,6 +11599,22 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4e95bed8-6d15-4403-ad70-a53422338dca">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C4EA295FB1FB9547A73C9F5819D6E613" ma:contentTypeVersion="23" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="fb09b8f9996d29818860aca561f17aea">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4e95bed8-6d15-4403-ad70-a53422338dca" xmlns:ns3="10d3344f-2d16-43d9-a145-97142f5cb288" xmlns:ns4="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f29125cba2118f3064d103e6e0ba85ce" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11880,7 +11899,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -11889,23 +11908,26 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4e95bed8-6d15-4403-ad70-a53422338dca">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFBB421F-7112-4B85-A662-9379706C03DC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="10d3344f-2d16-43d9-a145-97142f5cb288"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="4e95bed8-6d15-4403-ad70-a53422338dca"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FE7204C-46E3-4193-934C-CAD2C90BC68A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11926,22 +11948,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0EF40A6-8528-4994-A94E-1AE934020AF5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFBB421F-7112-4B85-A662-9379706C03DC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4e95bed8-6d15-4403-ad70-a53422338dca"/>
-    <ds:schemaRef ds:uri="d045ab76-3bb7-45f5-ab41-d7b04aa0dc94"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>